--- a/files/港岛-北角-君誉峰.xlsx
+++ b/files/港岛-北角-君誉峰.xlsx
@@ -764,7 +764,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2021-06-23</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2021-08-08</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2018-07-11</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2022-01-26</t>
+          <t>2022-01-27</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
+          <t>2020-08-21</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2021-07-04</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2020-12-23</t>
+          <t>2020-12-24</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2021-03-07</t>
+          <t>2021-03-08</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2021-01-05</t>
+          <t>2021-01-06</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2020-05-20</t>
+          <t>2020-05-21</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2021-03-07</t>
+          <t>2021-03-08</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2021-01-14</t>
+          <t>2021-01-15</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-02</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2021-03-03</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-06-02</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2019-05-09</t>
+          <t>2019-05-10</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2021-07-04</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2020-06-04</t>
+          <t>2020-06-05</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2021-01-28</t>
+          <t>2021-01-29</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2020-12-21</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2020-04-23</t>
+          <t>2020-04-24</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2019-07-23</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2021-02-07</t>
+          <t>2021-02-08</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2018-06-27</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2021-03-15</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2018-08-29</t>
+          <t>2018-08-30</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2019-05-02</t>
+          <t>2019-05-03</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2020-05-08</t>
+          <t>2020-05-09</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2019-06-11</t>
+          <t>2019-06-12</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2021-01-11</t>
+          <t>2021-01-12</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2020-01-05</t>
+          <t>2020-01-06</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2021-03-19</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
+          <t>2020-05-19</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2021-02-07</t>
+          <t>2021-02-08</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2018-05-16</t>
+          <t>2018-05-17</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2019-05-06</t>
+          <t>2019-05-07</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2019-04-07</t>
+          <t>2019-04-08</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2020-04-06</t>
+          <t>2020-04-07</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2021-02-02</t>
+          <t>2021-02-03</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2021-01-13</t>
+          <t>2021-01-14</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2020-01-07</t>
+          <t>2020-01-08</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2020-11-29</t>
+          <t>2020-11-30</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2021-04-28</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2018-04-16</t>
+          <t>2018-04-17</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2019-05-15</t>
+          <t>2019-05-16</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2019-03-17</t>
+          <t>2019-03-18</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2021-02-23</t>
+          <t>2021-02-24</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2020-04-14</t>
+          <t>2020-04-15</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2020-03-08</t>
+          <t>2020-03-09</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-08-18</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2019-12-18</t>
+          <t>2019-12-19</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2021-01-11</t>
+          <t>2021-01-12</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2020-04-08</t>
+          <t>2020-04-09</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2018-04-19</t>
+          <t>2018-04-20</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2019-06-05</t>
+          <t>2019-06-06</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2018-04-17</t>
+          <t>2018-04-18</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2020-11-29</t>
+          <t>2020-11-30</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2020-03-23</t>
+          <t>2020-03-24</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2019-12-23</t>
+          <t>2019-12-24</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2021-02-02</t>
+          <t>2021-02-03</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2020-04-08</t>
+          <t>2020-04-09</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2021-01-28</t>
+          <t>2021-01-29</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2020-02-18</t>
+          <t>2020-02-19</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2018-04-18</t>
+          <t>2018-04-19</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2018-04-02</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2018-06-27</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2020-03-17</t>
+          <t>2020-03-18</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2020-10-11</t>
+          <t>2020-10-12</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2020-04-27</t>
+          <t>2020-04-28</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
+          <t>2019-09-23</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2021-01-19</t>
+          <t>2021-01-20</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2019-05-17</t>
+          <t>2019-05-18</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
+          <t>2021-05-04</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2018-03-27</t>
+          <t>2018-03-28</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2021-05-14</t>
+          <t>2021-05-15</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2018-04-05</t>
+          <t>2018-04-06</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2018-06-06</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2020-10-04</t>
+          <t>2020-10-05</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2020-03-12</t>
+          <t>2020-03-13</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2019-08-08</t>
+          <t>2019-08-09</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2020-01-21</t>
+          <t>2020-01-22</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
+          <t>2019-09-23</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2021-02-03</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-08-02</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2019-06-03</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2020-12-15</t>
+          <t>2020-12-16</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2018-03-15</t>
+          <t>2018-03-16</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2021-05-04</t>
+          <t>2021-05-05</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2018-02-28</t>
+          <t>2018-03-01</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2018-05-24</t>
+          <t>2018-05-25</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2019-12-29</t>
+          <t>2019-12-30</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2020-03-03</t>
+          <t>2020-03-04</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2019-06-27</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2020-02-04</t>
+          <t>2020-02-05</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2019-07-21</t>
+          <t>2019-07-22</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2020-05-20</t>
+          <t>2020-05-21</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2019-07-30</t>
+          <t>2019-07-31</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2019-05-09</t>
+          <t>2019-05-10</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2020-09-18</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2018-03-20</t>
+          <t>2018-03-21</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2018-05-24</t>
+          <t>2018-05-25</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2018-05-23</t>
+          <t>2018-05-24</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2020-06-11</t>
+          <t>2020-06-12</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2020-01-22</t>
+          <t>2020-01-23</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2019-07-08</t>
+          <t>2019-07-09</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2020-03-04</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2019-07-08</t>
+          <t>2019-07-09</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2021-01-14</t>
+          <t>2021-01-15</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2019-07-23</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2019-05-27</t>
+          <t>2019-05-28</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2020-05-21</t>
+          <t>2020-05-22</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2018-03-07</t>
+          <t>2018-03-08</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2021-03-13</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2018-07-26</t>
+          <t>2018-07-27</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2018-02-25</t>
+          <t>2018-02-26</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2019-07-07</t>
+          <t>2019-07-08</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2020-01-08</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9530,7 +9530,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2019-05-26</t>
+          <t>2019-05-27</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2020-01-12</t>
+          <t>2020-01-13</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2019-07-08</t>
+          <t>2019-07-09</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
+          <t>2020-06-03</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2019-07-23</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2019-05-27</t>
+          <t>2019-05-28</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9902,7 +9902,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2018-02-27</t>
+          <t>2018-02-28</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2018-07-08</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2018-02-26</t>
+          <t>2018-02-27</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2019-05-29</t>
+          <t>2019-05-30</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2020-01-08</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2019-05-28</t>
+          <t>2019-05-29</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10398,7 +10398,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2019-12-23</t>
+          <t>2019-12-24</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2019-05-26</t>
+          <t>2019-05-27</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2019-03-06</t>
+          <t>2019-03-07</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2020-05-07</t>
+          <t>2020-05-08</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2018-02-26</t>
+          <t>2018-02-27</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2021-03-31</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2018-08-02</t>
+          <t>2018-08-03</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2018-05-08</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2019-05-20</t>
+          <t>2019-05-21</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2020-01-05</t>
+          <t>2020-01-06</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2019-05-28</t>
+          <t>2019-05-29</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2019-12-29</t>
+          <t>2019-12-30</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2019-05-26</t>
+          <t>2019-05-27</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-02-02</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
+          <t>2019-07-25</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2019-05-14</t>
+          <t>2019-05-15</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2020-03-23</t>
+          <t>2020-03-24</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2018-02-27</t>
+          <t>2018-02-28</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
+          <t>2021-05-13</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2019-03-27</t>
+          <t>2019-03-28</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2018-05-23</t>
+          <t>2018-05-24</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2019-05-27</t>
+          <t>2019-05-28</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2020-02-02</t>
+          <t>2020-02-03</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2019-05-28</t>
+          <t>2019-05-29</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2020-02-04</t>
+          <t>2020-02-05</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2019-05-28</t>
+          <t>2019-05-29</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2020-12-22</t>
+          <t>2020-12-23</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2019-05-09</t>
+          <t>2019-05-10</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12320,7 +12320,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2020-03-03</t>
+          <t>2020-03-04</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2018-02-28</t>
+          <t>2018-03-01</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2019-05-06</t>
+          <t>2019-05-07</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2018-03-13</t>
+          <t>2018-03-14</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2019-05-09</t>
+          <t>2019-05-10</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2020-01-16</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2019-05-20</t>
+          <t>2019-05-21</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12816,7 +12816,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2020-02-04</t>
+          <t>2020-02-05</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2019-05-30</t>
+          <t>2019-05-31</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -12940,7 +12940,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
+          <t>2020-05-19</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2019-07-12</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2019-05-05</t>
+          <t>2019-05-06</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13126,7 +13126,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2020-01-22</t>
+          <t>2020-01-23</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2018-02-27</t>
+          <t>2018-02-28</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2018-08-14</t>
+          <t>2018-08-15</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2018-02-26</t>
+          <t>2018-02-27</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2019-05-27</t>
+          <t>2019-05-28</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2020-01-05</t>
+          <t>2020-01-06</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2019-05-26</t>
+          <t>2019-05-27</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13622,7 +13622,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2020-02-04</t>
+          <t>2020-02-05</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13684,7 +13684,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2019-06-27</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13746,7 +13746,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
+          <t>2020-06-03</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2019-07-09</t>
+          <t>2019-07-10</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2019-03-07</t>
+          <t>2019-03-08</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -13932,7 +13932,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2020-01-08</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -13994,7 +13994,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2018-02-26</t>
+          <t>2018-02-27</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2018-06-01</t>
+          <t>2018-06-02</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14180,7 +14180,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2018-04-23</t>
+          <t>2018-04-24</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2019-02-10</t>
+          <t>2019-02-11</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2020-01-05</t>
+          <t>2020-01-06</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2019-05-26</t>
+          <t>2019-05-27</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2020-02-04</t>
+          <t>2020-02-05</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14490,7 +14490,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2019-05-15</t>
+          <t>2019-05-16</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
+          <t>2019-07-19</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-05-02</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14800,7 +14800,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2018-02-27</t>
+          <t>2018-02-28</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2021-03-08</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2018-08-24</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -14986,7 +14986,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2018-04-19</t>
+          <t>2018-04-20</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-05-02</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2020-01-02</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2019-05-15</t>
+          <t>2019-05-16</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2020-02-15</t>
+          <t>2020-02-16</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15296,7 +15296,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2019-06-27</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15358,7 +15358,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2021-01-13</t>
+          <t>2021-01-14</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
+          <t>2019-06-24</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-05-02</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15544,7 +15544,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2019-10-21</t>
+          <t>2019-10-22</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15606,7 +15606,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2018-02-28</t>
+          <t>2018-03-01</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15668,7 +15668,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2021-03-31</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2019-03-03</t>
+          <t>2019-03-04</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2018-02-25</t>
+          <t>2018-02-26</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15854,7 +15854,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2019-04-03</t>
+          <t>2019-04-04</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -15916,7 +15916,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2020-01-05</t>
+          <t>2020-01-06</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -15978,7 +15978,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2019-05-04</t>
+          <t>2019-05-05</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2019-12-14</t>
+          <t>2019-12-15</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16102,7 +16102,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2019-06-27</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2020-12-22</t>
+          <t>2020-12-23</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2019-06-21</t>
+          <t>2019-06-22</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16288,7 +16288,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2019-04-25</t>
+          <t>2019-04-26</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16350,7 +16350,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2019-12-23</t>
+          <t>2019-12-24</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16412,7 +16412,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2018-01-29</t>
+          <t>2018-01-30</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16536,7 +16536,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2019-01-14</t>
+          <t>2019-01-15</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2018-02-14</t>
+          <t>2018-02-15</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16660,7 +16660,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2019-04-22</t>
+          <t>2019-04-23</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2020-01-20</t>
+          <t>2020-01-21</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2019-05-26</t>
+          <t>2019-05-27</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16846,7 +16846,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2020-02-09</t>
+          <t>2020-02-10</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -16908,7 +16908,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2019-05-26</t>
+          <t>2019-05-27</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -16970,7 +16970,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2020-04-26</t>
+          <t>2020-04-27</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2019-07-12</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2018-10-21</t>
+          <t>2018-10-22</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2019-10-21</t>
+          <t>2019-10-22</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17218,7 +17218,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2018-02-26</t>
+          <t>2018-02-27</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17342,7 +17342,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2018-02-26</t>
+          <t>2018-02-27</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17404,7 +17404,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17466,7 +17466,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2019-04-28</t>
+          <t>2019-04-29</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2020-01-02</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17590,7 +17590,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2019-05-26</t>
+          <t>2019-05-27</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17652,7 +17652,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2020-03-02</t>
+          <t>2020-03-03</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17714,7 +17714,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17776,7 +17776,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17838,7 +17838,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2019-07-12</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2019-05-05</t>
+          <t>2019-05-06</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -17962,7 +17962,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2019-10-03</t>
+          <t>2019-10-04</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18024,7 +18024,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2021-02-11</t>
+          <t>2021-02-12</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18086,7 +18086,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18148,7 +18148,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2020-07-21</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18367,7 +18367,7 @@
           <t>A | 419呎 (2房)
 $1928万
 $46,014/呎
-(22年-01月-26日)</t>
+(22年-01月-27日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -18375,7 +18375,7 @@
           <t>B | 248呎 (1房)
 $1240万
 $50,000/呎
-(18年-07月-11日)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -18383,7 +18383,7 @@
           <t>C | 248呎 (1房)
 $1250万
 $50,403/呎
-(21年-08月-08日)</t>
+(21年-08月-09日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -18399,7 +18399,7 @@
           <t>E | 230呎 (1房)
 $698万
 $30,369/呎
-(21年-06月-23日)</t>
+(21年-06月-24日)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -18423,7 +18423,7 @@
           <t>H | 230呎 (1房)
 $702万
 $30,507/呎
-(21年-06月-24日)</t>
+(21年-06月-25日)</t>
         </is>
       </c>
       <c r="J5" s="22" t="inlineStr"/>
@@ -18443,7 +18443,7 @@
           <t>A | 365呎 (2房)
 $1063万
 $29,113/呎
-(20年-06月-01日)</t>
+(20年-06月-02日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -18451,7 +18451,7 @@
           <t>B | 288呎 (1房)
 $838万
 $29,097/呎
-(21年-03月-02日)</t>
+(21年-03月-03日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -18459,7 +18459,7 @@
           <t>C | 181呎 (开放式)
 $575万
 $31,749/呎
-(20年-12月-01日)</t>
+(20年-12月-02日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -18467,7 +18467,7 @@
           <t>D | 205呎 (开放式)
 $620万
 $30,224/呎
-(21年-01月-14日)</t>
+(21年-01月-15日)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -18483,7 +18483,7 @@
           <t>F | 181呎 (开放式)
 $574万
 $31,726/呎
-(21年-02月-25日)</t>
+(21年-02月-26日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -18491,7 +18491,7 @@
           <t>G | 287呎 (1房)
 $823万
 $28,667/呎
-(21年-03月-07日)</t>
+(21年-03月-08日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -18499,7 +18499,7 @@
           <t>H | 365呎 (2房)
 $1056万
 $28,922/呎
-(20年-05月-20日)</t>
+(20年-05月-21日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -18507,7 +18507,7 @@
           <t>J | 258呎 (1房)
 $733万
 $28,409/呎
-(21年-01月-05日)</t>
+(21年-01月-06日)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -18515,7 +18515,7 @@
           <t>K | 257呎 (1房)
 $762万
 $29,640/呎
-(21年-03月-07日)</t>
+(21年-03月-08日)</t>
         </is>
       </c>
       <c r="L6" s="20" t="inlineStr">
@@ -18523,7 +18523,7 @@
           <t>L | 250呎 (1房)
 $700万
 $27,997/呎
-(20年-12月-23日)</t>
+(20年-12月-24日)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -18531,7 +18531,7 @@
           <t>M | 263呎 (1房)
 $777万
 $29,545/呎
-(21年-07月-04日)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -18539,7 +18539,7 @@
           <t>N | 258呎 (1房)
 $769万
 $29,792/呎
-(20年-08月-20日)</t>
+(20年-08月-21日)</t>
         </is>
       </c>
     </row>
@@ -18554,7 +18554,7 @@
           <t>A | 365呎 (2房)
 $1031万
 $28,240/呎
-(18年-08月-29日)</t>
+(18年-08月-30日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -18562,7 +18562,7 @@
           <t>B | 288呎 (1房)
 $815万
 $28,283/呎
-(21年-03月-15日)</t>
+(21年-03月-16日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -18570,7 +18570,7 @@
           <t>C | 181呎 (开放式)
 $587万
 $32,436/呎
-(18年-06月-27日)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -18578,7 +18578,7 @@
           <t>D | 205呎 (开放式)
 $607万
 $29,634/呎
-(21年-02月-07日)</t>
+(21年-02月-08日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -18594,7 +18594,7 @@
           <t>F | 181呎 (开放式)
 $571万
 $31,533/呎
-(19年-07月-23日)</t>
+(19年-07月-24日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -18602,7 +18602,7 @@
           <t>G | 288呎 (1房)
 $801万
 $27,823/呎
-(21年-04月-07日)</t>
+(21年-04月-08日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -18610,7 +18610,7 @@
           <t>H | 365呎 (2房)
 $1057万
 $28,948/呎
-(20年-04月-23日)</t>
+(20年-04月-24日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -18618,7 +18618,7 @@
           <t>J | 258呎 (1房)
 $726万
 $28,156/呎
-(20年-12月-21日)</t>
+(20年-12月-22日)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -18626,7 +18626,7 @@
           <t>K | 257呎 (1房)
 $747万
 $29,073/呎
-(21年-01月-28日)</t>
+(21年-01月-29日)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -18634,7 +18634,7 @@
           <t>L | 250呎 (1房)
 $694万
 $27,746/呎
-(20年-06月-04日)</t>
+(20年-06月-05日)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -18642,7 +18642,7 @@
           <t>M | 263呎 (1房)
 $762万
 $28,972/呎
-(21年-07月-04日)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -18650,7 +18650,7 @@
           <t>N | 258呎 (1房)
 $761万
 $29,506/呎
-(19年-05月-09日)</t>
+(19年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -18665,7 +18665,7 @@
           <t>A | 365呎 (2房)
 $1031万
 $28,252/呎
-(19年-05月-06日)</t>
+(19年-05月-07日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -18673,7 +18673,7 @@
           <t>B | 288呎 (1房)
 $799万
 $27,743/呎
-(21年-03月-22日)</t>
+(21年-03月-23日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -18681,7 +18681,7 @@
           <t>C | 181呎 (开放式)
 $570万
 $31,478/呎
-(18年-05月-16日)</t>
+(18年-05月-17日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -18689,7 +18689,7 @@
           <t>D | 205呎 (开放式)
 $608万
 $29,644/呎
-(21年-02月-07日)</t>
+(21年-02月-08日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -18705,7 +18705,7 @@
           <t>F | 181呎 (开放式)
 $561万
 $31,008/呎
-(20年-05月-18日)</t>
+(20年-05月-19日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -18713,7 +18713,7 @@
           <t>G | 288呎 (1房)
 $796万
 $27,643/呎
-(21年-03月-18日)</t>
+(21年-03月-19日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -18721,7 +18721,7 @@
           <t>H | 365呎 (2房)
 $1015万
 $27,806/呎
-(20年-01月-05日)</t>
+(20年-01月-06日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -18729,7 +18729,7 @@
           <t>J | 258呎 (1房)
 $712万
 $27,598/呎
-(21年-01月-11日)</t>
+(21年-01月-12日)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -18737,7 +18737,7 @@
           <t>K | 257呎 (1房)
 $740万
 $28,789/呎
-(19年-06月-11日)</t>
+(19年-06月-12日)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -18745,7 +18745,7 @@
           <t>L | 250呎 (1房)
 $701万
 $28,045/呎
-(20年-05月-08日)</t>
+(20年-05月-09日)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -18753,7 +18753,7 @@
           <t>M | 263呎 (1房)
 $754万
 $28,683/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -18761,7 +18761,7 @@
           <t>N | 258呎 (1房)
 $754万
 $29,220/呎
-(19年-05月-02日)</t>
+(19年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -18776,7 +18776,7 @@
           <t>A | 365呎 (2房)
 $1010万
 $27,682/呎
-(19年-05月-15日)</t>
+(19年-05月-16日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -18784,7 +18784,7 @@
           <t>B | 288呎 (1房)
 $792万
 $27,483/呎
-(21年-04月-07日)</t>
+(21年-04月-08日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -18792,7 +18792,7 @@
           <t>C | 181呎 (开放式)
 $541万
 $29,914/呎
-(18年-04月-16日)</t>
+(18年-04月-17日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -18800,7 +18800,7 @@
           <t>D | 205呎 (开放式)
 $602万
 $29,346/呎
-(21年-04月-28日)</t>
+(21年-04月-29日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -18816,7 +18816,7 @@
           <t>F | 181呎 (开放式)
 $552万
 $30,481/呎
-(20年-11月-29日)</t>
+(20年-11月-30日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -18824,7 +18824,7 @@
           <t>G | 288呎 (1房)
 $791万
 $27,460/呎
-(21年-04月-06日)</t>
+(21年-04月-07日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -18832,7 +18832,7 @@
           <t>H | 365呎 (2房)
 $1015万
 $27,816/呎
-(20年-01月-07日)</t>
+(20年-01月-08日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -18840,7 +18840,7 @@
           <t>J | 258呎 (1房)
 $705万
 $27,327/呎
-(21年-01月-13日)</t>
+(21年-01月-14日)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -18848,7 +18848,7 @@
           <t>K | 257呎 (1房)
 $740万
 $28,806/呎
-(21年-02月-02日)</t>
+(21年-02月-03日)</t>
         </is>
       </c>
       <c r="L9" s="20" t="inlineStr">
@@ -18856,7 +18856,7 @@
           <t>L | 250呎 (1房)
 $694万
 $27,768/呎
-(20年-04月-06日)</t>
+(20年-04月-07日)</t>
         </is>
       </c>
       <c r="M9" s="20" t="inlineStr">
@@ -18864,7 +18864,7 @@
           <t>M | 263呎 (1房)
 $747万
 $28,395/呎
-(21年-08月-23日)</t>
+(21年-08月-24日)</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -18872,7 +18872,7 @@
           <t>N | 258呎 (1房)
 $747万
 $28,935/呎
-(19年-04月-07日)</t>
+(19年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -18887,7 +18887,7 @@
           <t>A | 365呎 (2房)
 $1035万
 $28,355/呎
-(19年-06月-05日)</t>
+(19年-06月-06日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -18895,7 +18895,7 @@
           <t>B | 288呎 (1房)
 $778万
 $27,020/呎
-(21年-04月-07日)</t>
+(21年-04月-08日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -18903,7 +18903,7 @@
           <t>C | 181呎 (开放式)
 $538万
 $29,712/呎
-(18年-04月-19日)</t>
+(18年-04月-20日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -18911,7 +18911,7 @@
           <t>D | 205呎 (开放式)
 $598万
 $29,147/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -18927,7 +18927,7 @@
           <t>F | 181呎 (开放式)
 $554万
 $30,595/呎
-(20年-04月-08日)</t>
+(20年-04月-09日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -18935,7 +18935,7 @@
           <t>G | 288呎 (1房)
 $786万
 $27,280/呎
-(21年-01月-11日)</t>
+(21年-01月-12日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -18943,7 +18943,7 @@
           <t>H | 365呎 (2房)
 $988万
 $27,067/呎
-(19年-12月-18日)</t>
+(19年-12月-19日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -18951,7 +18951,7 @@
           <t>J | 258呎 (1房)
 $715万
 $27,713/呎
-(20年-08月-17日)</t>
+(20年-08月-18日)</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
@@ -18959,7 +18959,7 @@
           <t>K | 257呎 (1房)
 $751万
 $29,203/呎
-(20年-03月-08日)</t>
+(20年-03月-09日)</t>
         </is>
       </c>
       <c r="L10" s="20" t="inlineStr">
@@ -18967,7 +18967,7 @@
           <t>L | 250呎 (1房)
 $669万
 $26,746/呎
-(20年-04月-14日)</t>
+(20年-04月-15日)</t>
         </is>
       </c>
       <c r="M10" s="20" t="inlineStr">
@@ -18975,7 +18975,7 @@
           <t>M | 263呎 (1房)
 $742万
 $28,205/呎
-(21年-02月-23日)</t>
+(21年-02月-24日)</t>
         </is>
       </c>
       <c r="N10" s="20" t="inlineStr">
@@ -18983,7 +18983,7 @@
           <t>N | 258呎 (1房)
 $734万
 $28,450/呎
-(19年-03月-17日)</t>
+(19年-03月-18日)</t>
         </is>
       </c>
     </row>
@@ -18998,7 +18998,7 @@
           <t>A | 365呎 (2房)
 $1007万
 $27,593/呎
-(18年-04月-02日)</t>
+(18年-04月-03日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -19006,7 +19006,7 @@
           <t>B | 288呎 (1房)
 $773万
 $26,837/呎
-(21年-05月-16日)</t>
+(21年-05月-17日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -19014,7 +19014,7 @@
           <t>C | 181呎 (开放式)
 $556万
 $30,735/呎
-(18年-04月-18日)</t>
+(18年-04月-19日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -19022,7 +19022,7 @@
           <t>D | 205呎 (开放式)
 $600万
 $29,247/呎
-(20年-02月-18日)</t>
+(20年-02月-19日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -19030,7 +19030,7 @@
           <t>E | 205呎 (开放式)
 $605万
 $29,507/呎
-(21年-01月-28日)</t>
+(21年-01月-29日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -19038,7 +19038,7 @@
           <t>F | 181呎 (开放式)
 $550万
 $30,386/呎
-(20年-04月-08日)</t>
+(20年-04月-09日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -19046,7 +19046,7 @@
           <t>G | 288呎 (1房)
 $780万
 $27,100/呎
-(21年-02月-02日)</t>
+(21年-02月-03日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -19054,7 +19054,7 @@
           <t>H | 365呎 (2房)
 $981万
 $26,885/呎
-(19年-12月-23日)</t>
+(19年-12月-24日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -19062,7 +19062,7 @@
           <t>J | 258呎 (1房)
 $696万
 $26,966/呎
-(20年-07月-15日)</t>
+(20年-07月-16日)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -19070,7 +19070,7 @@
           <t>K | 257呎 (1房)
 $723万
 $28,131/呎
-(20年-07月-15日)</t>
+(20年-07月-16日)</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
@@ -19078,7 +19078,7 @@
           <t>L | 250呎 (1房)
 $671万
 $26,846/呎
-(20年-03月-23日)</t>
+(20年-03月-24日)</t>
         </is>
       </c>
       <c r="M11" s="20" t="inlineStr">
@@ -19086,7 +19086,7 @@
           <t>M | 263呎 (1房)
 $744万
 $28,303/呎
-(20年-11月-29日)</t>
+(20年-11月-30日)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
@@ -19094,7 +19094,7 @@
           <t>N | 258呎 (1房)
 $737万
 $28,555/呎
-(18年-04月-17日)</t>
+(18年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -19109,7 +19109,7 @@
           <t>A | 365呎 (2房)
 $990万
 $27,122/呎
-(18年-04月-05日)</t>
+(18年-04月-06日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -19117,7 +19117,7 @@
           <t>B | 287呎 (1房)
 $776万
 $27,028/呎
-(21年-05月-14日)</t>
+(21年-05月-15日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -19125,7 +19125,7 @@
           <t>C | 181呎 (开放式)
 $552万
 $30,525/呎
-(18年-03月-27日)</t>
+(18年-03月-28日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -19133,7 +19133,7 @@
           <t>D | 205呎 (开放式)
 $583万
 $28,453/呎
-(21年-05月-03日)</t>
+(21年-05月-04日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -19141,7 +19141,7 @@
           <t>E | 205呎 (开放式)
 $601万
 $29,310/呎
-(19年-05月-17日)</t>
+(19年-05月-18日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -19149,7 +19149,7 @@
           <t>F | 181呎 (开放式)
 $541万
 $29,871/呎
-(19年-07月-17日)</t>
+(19年-07月-18日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -19157,7 +19157,7 @@
           <t>G | 287呎 (1房)
 $783万
 $27,295/呎
-(21年-01月-19日)</t>
+(21年-01月-20日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -19165,7 +19165,7 @@
           <t>H | 365呎 (2房)
 $1005万
 $27,541/呎
-(19年-09月-22日)</t>
+(19年-09月-23日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -19173,7 +19173,7 @@
           <t>J | 258呎 (1房)
 $698万
 $27,066/呎
-(20年-04月-27日)</t>
+(20年-04月-28日)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -19181,7 +19181,7 @@
           <t>K | 257呎 (1房)
 $718万
 $27,941/呎
-(20年-10月-11日)</t>
+(20年-10月-12日)</t>
         </is>
       </c>
       <c r="L12" s="20" t="inlineStr">
@@ -19189,7 +19189,7 @@
           <t>L | 250呎 (1房)
 $660万
 $26,388/呎
-(20年-03月-17日)</t>
+(20年-03月-18日)</t>
         </is>
       </c>
       <c r="M12" s="20" t="inlineStr">
@@ -19197,7 +19197,7 @@
           <t>M | 263呎 (1房)
 $739万
 $28,112/呎
-(21年-02月-25日)</t>
+(21年-02月-26日)</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
@@ -19205,7 +19205,7 @@
           <t>N | 258呎 (1房)
 $732万
 $28,367/呎
-(18年-06月-27日)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -19220,7 +19220,7 @@
           <t>A | 365呎 (2房)
 $1004万
 $27,499/呎
-(18年-02月-28日)</t>
+(18年-03月-01日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -19228,7 +19228,7 @@
           <t>B | 287呎 (1房)
 $763万
 $26,569/呎
-(21年-05月-04日)</t>
+(21年-05月-05日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -19236,7 +19236,7 @@
           <t>C | 181呎 (开放式)
 $532万
 $29,405/呎
-(18年-03月-15日)</t>
+(18年-03月-16日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -19244,7 +19244,7 @@
           <t>D | 205呎 (开放式)
 $579万
 $28,257/呎
-(20年-12月-15日)</t>
+(20年-12月-16日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -19252,7 +19252,7 @@
           <t>E | 205呎 (开放式)
 $603万
 $29,412/呎
-(19年-06月-02日)</t>
+(19年-06月-03日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -19260,7 +19260,7 @@
           <t>F | 181呎 (开放式)
 $537万
 $29,670/呎
-(19年-08月-01日)</t>
+(19年-08月-02日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -19268,7 +19268,7 @@
           <t>G | 287呎 (1房)
 $770万
 $26,830/呎
-(21年-02月-03日)</t>
+(21年-02月-04日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -19276,7 +19276,7 @@
           <t>H | 365呎 (2房)
 $998万
 $27,354/呎
-(19年-09月-22日)</t>
+(19年-09月-23日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -19284,7 +19284,7 @@
           <t>J | 258呎 (1房)
 $694万
 $26,882/呎
-(20年-01月-21日)</t>
+(20年-01月-22日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -19292,7 +19292,7 @@
           <t>K | 257呎 (1房)
 $721万
 $28,043/呎
-(19年-08月-08日)</t>
+(19年-08月-09日)</t>
         </is>
       </c>
       <c r="L13" s="20" t="inlineStr">
@@ -19300,7 +19300,7 @@
           <t>L | 250呎 (1房)
 $655万
 $26,212/呎
-(20年-03月-12日)</t>
+(20年-03月-13日)</t>
         </is>
       </c>
       <c r="M13" s="20" t="inlineStr">
@@ -19308,7 +19308,7 @@
           <t>M | 263呎 (1房)
 $727万
 $27,628/呎
-(20年-10月-04日)</t>
+(20年-10月-05日)</t>
         </is>
       </c>
       <c r="N13" s="20" t="inlineStr">
@@ -19316,7 +19316,7 @@
           <t>N | 258呎 (1房)
 $727万
 $28,175/呎
-(18年-06月-05日)</t>
+(18年-06月-06日)</t>
         </is>
       </c>
     </row>
@@ -19331,7 +19331,7 @@
           <t>A | 365呎 (2房)
 $987万
 $27,030/呎
-(18年-05月-24日)</t>
+(18年-05月-25日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -19339,7 +19339,7 @@
           <t>B | 287呎 (1房)
 $757万
 $26,388/呎
-(21年-03月-16日)</t>
+(21年-03月-17日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -19347,7 +19347,7 @@
           <t>C | 181呎 (开放式)
 $528万
 $29,196/呎
-(18年-03月-20日)</t>
+(18年-03月-21日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -19355,7 +19355,7 @@
           <t>D | 205呎 (开放式)
 $581万
 $28,352/呎
-(20年-09月-17日)</t>
+(20年-09月-18日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -19363,7 +19363,7 @@
           <t>E | 205呎 (开放式)
 $599万
 $29,214/呎
-(19年-05月-09日)</t>
+(19年-05月-10日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -19371,7 +19371,7 @@
           <t>F | 181呎 (开放式)
 $539万
 $29,770/呎
-(19年-07月-30日)</t>
+(19年-07月-31日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -19379,7 +19379,7 @@
           <t>G | 288呎 (1房)
 $773万
 $26,833/呎
-(20年-05月-20日)</t>
+(20年-05月-21日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -19387,7 +19387,7 @@
           <t>H | 365呎 (2房)
 $962万
 $26,343/呎
-(19年-07月-21日)</t>
+(19年-07月-22日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -19395,7 +19395,7 @@
           <t>J | 258呎 (1房)
 $682万
 $26,426/呎
-(20年-02月-04日)</t>
+(20年-02月-05日)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -19403,7 +19403,7 @@
           <t>K | 257呎 (1房)
 $716万
 $27,851/呎
-(19年-06月-27日)</t>
+(19年-06月-28日)</t>
         </is>
       </c>
       <c r="L14" s="20" t="inlineStr">
@@ -19411,7 +19411,7 @@
           <t>L | 250呎 (1房)
 $658万
 $26,303/呎
-(20年-03月-03日)</t>
+(20年-03月-04日)</t>
         </is>
       </c>
       <c r="M14" s="20" t="inlineStr">
@@ -19419,7 +19419,7 @@
           <t>M | 263呎 (1房)
 $729万
 $27,721/呎
-(19年-12月-29日)</t>
+(19年-12月-30日)</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -19427,7 +19427,7 @@
           <t>N | 258呎 (1房)
 $722万
 $27,987/呎
-(18年-05月-24日)</t>
+(18年-05月-25日)</t>
         </is>
       </c>
     </row>
@@ -19442,7 +19442,7 @@
           <t>A | 365呎 (2房)
 $966万
 $26,472/呎
-(18年-07月-26日)</t>
+(18年-07月-27日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -19450,7 +19450,7 @@
           <t>B | 288呎 (1房)
 $749万
 $26,023/呎
-(21年-03月-12日)</t>
+(21年-03月-13日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -19458,7 +19458,7 @@
           <t>C | 181呎 (开放式)
 $518万
 $28,593/呎
-(18年-03月-07日)</t>
+(18年-03月-08日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -19466,7 +19466,7 @@
           <t>D | 205呎 (开放式)
 $569万
 $27,765/呎
-(20年-05月-21日)</t>
+(20年-05月-22日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -19474,7 +19474,7 @@
           <t>E | 205呎 (开放式)
 $593万
 $28,911/呎
-(19年-05月-27日)</t>
+(19年-05月-28日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -19482,7 +19482,7 @@
           <t>F | 181呎 (开放式)
 $533万
 $29,464/呎
-(19年-07月-23日)</t>
+(19年-07月-24日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -19490,7 +19490,7 @@
           <t>G | 288呎 (1房)
 $757万
 $26,287/呎
-(21年-01月-14日)</t>
+(21年-01月-15日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -19498,7 +19498,7 @@
           <t>H | 365呎 (2房)
 $962万
 $26,344/呎
-(19年-07月-08日)</t>
+(19年-07月-09日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -19506,7 +19506,7 @@
           <t>J | 258呎 (1房)
 $682万
 $26,427/呎
-(20年-03月-04日)</t>
+(20年-03月-05日)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -19514,7 +19514,7 @@
           <t>K | 257呎 (1房)
 $708万
 $27,564/呎
-(19年-07月-08日)</t>
+(19年-07月-09日)</t>
         </is>
       </c>
       <c r="L15" s="20" t="inlineStr">
@@ -19522,7 +19522,7 @@
           <t>L | 250呎 (1房)
 $644万
 $25,766/呎
-(20年-01月-22日)</t>
+(20年-01月-23日)</t>
         </is>
       </c>
       <c r="M15" s="20" t="inlineStr">
@@ -19530,7 +19530,7 @@
           <t>M | 263呎 (1房)
 $714万
 $27,150/呎
-(20年-06月-11日)</t>
+(20年-06月-12日)</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -19538,7 +19538,7 @@
           <t>N | 258呎 (1房)
 $715万
 $27,701/呎
-(18年-05月-23日)</t>
+(18年-05月-24日)</t>
         </is>
       </c>
     </row>
@@ -19553,7 +19553,7 @@
           <t>A | 365呎 (2房)
 $999万
 $27,381/呎
-(18年-07月-08日)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -19561,7 +19561,7 @@
           <t>B | 288呎 (1房)
 $744万
 $25,843/呎
-(21年-06月-10日)</t>
+(21年-06月-11日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -19569,7 +19569,7 @@
           <t>C | 181呎 (开放式)
 $514万
 $28,386/呎
-(18年-02月-27日)</t>
+(18年-02月-28日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -19577,7 +19577,7 @@
           <t>D | 205呎 (开放式)
 $571万
 $27,856/呎
-(20年-05月-17日)</t>
+(20年-05月-18日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -19585,7 +19585,7 @@
           <t>E | 205呎 (开放式)
 $595万
 $29,008/呎
-(19年-05月-27日)</t>
+(19年-05月-28日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -19593,7 +19593,7 @@
           <t>F | 181呎 (开放式)
 $524万
 $28,954/呎
-(19年-07月-23日)</t>
+(19年-07月-24日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -19601,7 +19601,7 @@
           <t>G | 288呎 (1房)
 $760万
 $26,375/呎
-(20年-06月-02日)</t>
+(20年-06月-03日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -19609,7 +19609,7 @@
           <t>H | 365呎 (2房)
 $955万
 $26,161/呎
-(19年-07月-08日)</t>
+(19年-07月-09日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -19617,7 +19617,7 @@
           <t>J | 258呎 (1房)
 $691万
 $26,788/呎
-(20年-01月-12日)</t>
+(20年-01月-13日)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -19625,7 +19625,7 @@
           <t>K | 257呎 (1房)
 $696万
 $27,093/呎
-(19年-05月-26日)</t>
+(19年-05月-27日)</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr">
@@ -19633,7 +19633,7 @@
           <t>L | 250呎 (1房)
 $646万
 $25,852/呎
-(20年-01月-08日)</t>
+(20年-01月-09日)</t>
         </is>
       </c>
       <c r="M16" s="20" t="inlineStr">
@@ -19641,7 +19641,7 @@
           <t>M | 263呎 (1房)
 $709万
 $26,957/呎
-(19年-07月-07日)</t>
+(19年-07月-08日)</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
@@ -19649,7 +19649,7 @@
           <t>N | 258呎 (1房)
 $717万
 $27,793/呎
-(18年-02月-25日)</t>
+(18年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -19664,7 +19664,7 @@
           <t>A | 365呎 (2房)
 $953万
 $26,099/呎
-(18年-08月-02日)</t>
+(18年-08月-03日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -19672,7 +19672,7 @@
           <t>B | 288呎 (1房)
 $739万
 $25,663/呎
-(21年-03月-31日)</t>
+(21年-04月-01日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -19680,7 +19680,7 @@
           <t>C | 181呎 (开放式)
 $515万
 $28,478/呎
-(18年-02月-26日)</t>
+(18年-02月-27日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -19688,7 +19688,7 @@
           <t>D | 205呎 (开放式)
 $567万
 $27,657/呎
-(20年-05月-07日)</t>
+(20年-05月-08日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -19696,7 +19696,7 @@
           <t>E | 205呎 (开放式)
 $578万
 $28,215/呎
-(19年-03月-06日)</t>
+(19年-03月-07日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -19704,7 +19704,7 @@
           <t>F | 181呎 (开放式)
 $520万
 $28,752/呎
-(19年-07月-16日)</t>
+(19年-07月-17日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -19712,7 +19712,7 @@
           <t>G | 288呎 (1房)
 $747万
 $25,923/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -19720,7 +19720,7 @@
           <t>H | 365呎 (2房)
 $968万
 $26,516/呎
-(19年-05月-26日)</t>
+(19年-05月-27日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -19728,7 +19728,7 @@
           <t>J | 258呎 (1房)
 $686万
 $26,600/呎
-(19年-12月-23日)</t>
+(19年-12月-24日)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -19736,7 +19736,7 @@
           <t>K | 257呎 (1房)
 $699万
 $27,183/呎
-(19年-05月-28日)</t>
+(19年-05月-29日)</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
@@ -19744,7 +19744,7 @@
           <t>L | 250呎 (1房)
 $648万
 $25,939/呎
-(20年-01月-08日)</t>
+(20年-01月-09日)</t>
         </is>
       </c>
       <c r="M17" s="20" t="inlineStr">
@@ -19752,7 +19752,7 @@
           <t>M | 263呎 (1房)
 $704万
 $26,767/呎
-(19年-05月-29日)</t>
+(19年-05月-30日)</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -19760,7 +19760,7 @@
           <t>N | 258呎 (1房)
 $698万
 $27,040/呎
-(18年-02月-26日)</t>
+(18年-02月-27日)</t>
         </is>
       </c>
     </row>
@@ -19775,7 +19775,7 @@
           <t>A | 365呎 (2房)
 $946万
 $25,915/呎
-(19年-03月-27日)</t>
+(19年-03月-28日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -19783,7 +19783,7 @@
           <t>B | 287呎 (1房)
 $734万
 $25,569/呎
-(21年-05月-12日)</t>
+(21年-05月-13日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -19791,7 +19791,7 @@
           <t>C | 181呎 (开放式)
 $512万
 $28,269/呎
-(18年-02月-27日)</t>
+(18年-02月-28日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -19799,7 +19799,7 @@
           <t>D | 205呎 (开放式)
 $557万
 $27,175/呎
-(20年-03月-23日)</t>
+(20年-03月-24日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -19807,7 +19807,7 @@
           <t>E | 205呎 (开放式)
 $580万
 $28,310/呎
-(19年-05月-14日)</t>
+(19年-05月-15日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -19815,7 +19815,7 @@
           <t>F | 181呎 (开放式)
 $527万
 $29,140/呎
-(19年-07月-24日)</t>
+(19年-07月-25日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -19823,7 +19823,7 @@
           <t>G | 288呎 (1房)
 $741万
 $25,743/呎
-(21年-02月-01日)</t>
+(21年-02月-02日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -19831,7 +19831,7 @@
           <t>H | 365呎 (2房)
 $942万
 $25,797/呎
-(19年-05月-26日)</t>
+(19年-05月-27日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -19839,7 +19839,7 @@
           <t>J | 258呎 (1房)
 $661万
 $25,615/呎
-(19年-12月-29日)</t>
+(19年-12月-30日)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -19847,7 +19847,7 @@
           <t>K | 257呎 (1房)
 $694万
 $26,994/呎
-(19年-05月-28日)</t>
+(19年-05月-29日)</t>
         </is>
       </c>
       <c r="L18" s="20" t="inlineStr">
@@ -19855,7 +19855,7 @@
           <t>L | 250呎 (1房)
 $637万
 $25,492/呎
-(20年-01月-05日)</t>
+(20年-01月-06日)</t>
         </is>
       </c>
       <c r="M18" s="20" t="inlineStr">
@@ -19863,7 +19863,7 @@
           <t>M | 263呎 (1房)
 $706万
 $26,850/呎
-(19年-05月-20日)</t>
+(19年-05月-21日)</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
@@ -19871,7 +19871,7 @@
           <t>N | 258呎 (1房)
 $700万
 $27,130/呎
-(18年-05月-08日)</t>
+(18年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -19886,7 +19886,7 @@
           <t>A | 365呎 (2房)
 $968万
 $26,532/呎
-(19年-05月-06日)</t>
+(19年-05月-07日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -19894,7 +19894,7 @@
           <t>B | 288呎 (1房)
 $736万
 $25,564/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -19902,7 +19902,7 @@
           <t>C | 181呎 (开放式)
 $503万
 $27,776/呎
-(18年-02月-28日)</t>
+(18年-03月-01日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -19910,7 +19910,7 @@
           <t>D | 205呎 (开放式)
 $559万
 $27,259/呎
-(20年-03月-03日)</t>
+(20年-03月-04日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -19918,7 +19918,7 @@
           <t>E | 205呎 (开放式)
 $574万
 $28,007/呎
-(19年-05月-09日)</t>
+(19年-05月-10日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -19926,7 +19926,7 @@
           <t>F | 181呎 (开放式)
 $509万
 $28,142/呎
-(19年-07月-16日)</t>
+(19年-07月-17日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -19934,7 +19934,7 @@
           <t>G | 287呎 (1房)
 $739万
 $25,734/呎
-(20年-12月-22日)</t>
+(20年-12月-23日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -19942,7 +19942,7 @@
           <t>H | 365呎 (2房)
 $935万
 $25,613/呎
-(19年-05月-28日)</t>
+(19年-05月-29日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -19950,7 +19950,7 @@
           <t>J | 258呎 (1房)
 $663万
 $25,701/呎
-(20年-02月-04日)</t>
+(20年-02月-05日)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -19958,7 +19958,7 @@
           <t>K | 257呎 (1房)
 $682万
 $26,525/呎
-(19年-05月-28日)</t>
+(19年-05月-29日)</t>
         </is>
       </c>
       <c r="L19" s="20" t="inlineStr">
@@ -19966,7 +19966,7 @@
           <t>L | 250呎 (1房)
 $646万
 $25,835/呎
-(20年-02月-02日)</t>
+(20年-02月-03日)</t>
         </is>
       </c>
       <c r="M19" s="20" t="inlineStr">
@@ -19974,7 +19974,7 @@
           <t>M | 263呎 (1房)
 $701万
 $26,658/呎
-(19年-05月-27日)</t>
+(19年-05月-28日)</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -19982,7 +19982,7 @@
           <t>N | 258呎 (1房)
 $695万
 $26,942/呎
-(18年-05月-23日)</t>
+(18年-05月-24日)</t>
         </is>
       </c>
     </row>
@@ -19997,7 +19997,7 @@
           <t>A | 365呎 (2房)
 $971万
 $26,605/呎
-(18年-08月-14日)</t>
+(18年-08月-15日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -20005,7 +20005,7 @@
           <t>B | 288呎 (1房)
 $723万
 $25,120/呎
-(21年-02月-25日)</t>
+(21年-02月-26日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -20013,7 +20013,7 @@
           <t>C | 181呎 (开放式)
 $504万
 $27,862/呎
-(18年-02月-27日)</t>
+(18年-02月-28日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -20021,7 +20021,7 @@
           <t>D | 205呎 (开放式)
 $555万
 $27,061/呎
-(20年-01月-22日)</t>
+(20年-01月-23日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -20029,7 +20029,7 @@
           <t>E | 205呎 (开放式)
 $574万
 $27,990/呎
-(19年-05月-05日)</t>
+(19年-05月-06日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -20037,7 +20037,7 @@
           <t>F | 181呎 (开放式)
 $512万
 $28,312/呎
-(19年-07月-11日)</t>
+(19年-07月-12日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -20045,7 +20045,7 @@
           <t>G | 288呎 (1房)
 $721万
 $25,020/呎
-(20年-05月-18日)</t>
+(20年-05月-19日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -20053,7 +20053,7 @@
           <t>H | 365呎 (2房)
 $938万
 $25,695/呎
-(19年-05月-30日)</t>
+(19年-05月-31日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -20061,7 +20061,7 @@
           <t>J | 258呎 (1房)
 $658万
 $25,517/呎
-(20年-02月-04日)</t>
+(20年-02月-05日)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -20069,7 +20069,7 @@
           <t>K | 257呎 (1房)
 $684万
 $26,613/呎
-(19年-05月-20日)</t>
+(19年-05月-21日)</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
@@ -20077,7 +20077,7 @@
           <t>L | 250呎 (1房)
 $622万
 $24,872/呎
-(20年-01月-16日)</t>
+(20年-01月-17日)</t>
         </is>
       </c>
       <c r="M20" s="20" t="inlineStr">
@@ -20085,7 +20085,7 @@
           <t>M | 263呎 (1房)
 $696万
 $26,463/呎
-(19年-05月-09日)</t>
+(19年-05月-10日)</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
@@ -20093,7 +20093,7 @@
           <t>N | 258呎 (1房)
 $690万
 $26,750/呎
-(18年-03月-13日)</t>
+(18年-03月-14日)</t>
         </is>
       </c>
     </row>
@@ -20108,7 +20108,7 @@
           <t>A | 365呎 (2房)
 $935万
 $25,619/呎
-(18年-06月-01日)</t>
+(18年-06月-02日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -20116,7 +20116,7 @@
           <t>B | 287呎 (1房)
 $718万
 $25,027/呎
-(21年-03月-16日)</t>
+(21年-03月-17日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -20124,7 +20124,7 @@
           <t>C | 181呎 (开放式)
 $501万
 $27,653/呎
-(18年-02月-26日)</t>
+(18年-02月-27日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -20132,7 +20132,7 @@
           <t>D | 205呎 (开放式)
 $556万
 $27,139/呎
-(20年-01月-08日)</t>
+(20年-01月-09日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -20140,7 +20140,7 @@
           <t>E | 205呎 (开放式)
 $575万
 $28,073/呎
-(19年-03月-07日)</t>
+(19年-03月-08日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -20148,7 +20148,7 @@
           <t>F | 181呎 (开放式)
 $504万
 $27,819/呎
-(19年-07月-09日)</t>
+(19年-07月-10日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -20156,7 +20156,7 @@
           <t>G | 288呎 (1房)
 $723万
 $25,099/呎
-(20年-06月-02日)</t>
+(20年-06月-03日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -20164,7 +20164,7 @@
           <t>H | 365呎 (2房)
 $922万
 $25,249/呎
-(19年-06月-27日)</t>
+(19年-06月-28日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -20172,7 +20172,7 @@
           <t>J | 258呎 (1房)
 $654万
 $25,337/呎
-(20年-02月-04日)</t>
+(20年-02月-05日)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -20180,7 +20180,7 @@
           <t>K | 257呎 (1房)
 $672万
 $26,148/呎
-(19年-05月-26日)</t>
+(19年-05月-27日)</t>
         </is>
       </c>
       <c r="L21" s="20" t="inlineStr">
@@ -20188,7 +20188,7 @@
           <t>L | 250呎 (1房)
 $617万
 $24,695/呎
-(20年-01月-05日)</t>
+(20年-01月-06日)</t>
         </is>
       </c>
       <c r="M21" s="20" t="inlineStr">
@@ -20196,7 +20196,7 @@
           <t>M | 263呎 (1房)
 $691万
 $26,267/呎
-(19年-05月-27日)</t>
+(19年-05月-28日)</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -20204,7 +20204,7 @@
           <t>N | 258呎 (1房)
 $685万
 $26,562/呎
-(18年-02月-26日)</t>
+(18年-02月-27日)</t>
         </is>
       </c>
     </row>
@@ -20219,7 +20219,7 @@
           <t>A | 365呎 (2房)
 $951万
 $26,052/呎
-(18年-08月-23日)</t>
+(18年-08月-24日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -20227,7 +20227,7 @@
           <t>B | 288呎 (1房)
 $716万
 $24,850/呎
-(21年-03月-08日)</t>
+(21年-03月-09日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -20235,7 +20235,7 @@
           <t>C | 181呎 (开放式)
 $494万
 $27,267/呎
-(18年-02月-27日)</t>
+(18年-02月-28日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -20243,7 +20243,7 @@
           <t>D | 205呎 (开放式)
 $554万
 $27,038/呎
-(19年-10月-31日)</t>
+(19年-11月-01日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -20251,7 +20251,7 @@
           <t>E | 205呎 (开放式)
 $556万
 $27,124/呎
-(19年-05月-01日)</t>
+(19年-05月-02日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -20259,7 +20259,7 @@
           <t>F | 181呎 (开放式)
 $496万
 $27,426/呎
-(19年-07月-18日)</t>
+(19年-07月-19日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -20267,7 +20267,7 @@
           <t>G | 288呎 (1房)
 $713万
 $24,750/呎
-(20年-10月-21日)</t>
+(20年-10月-22日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -20275,7 +20275,7 @@
           <t>H | 365呎 (2房)
 $918万
 $25,159/呎
-(19年-05月-15日)</t>
+(19年-05月-16日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -20283,7 +20283,7 @@
           <t>J | 258呎 (1房)
 $658万
 $25,503/呎
-(20年-02月-04日)</t>
+(20年-02月-05日)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -20291,7 +20291,7 @@
           <t>K | 257呎 (1房)
 $677万
 $26,326/呎
-(19年-05月-26日)</t>
+(19年-05月-27日)</t>
         </is>
       </c>
       <c r="L22" s="20" t="inlineStr">
@@ -20299,7 +20299,7 @@
           <t>L | 250呎 (1房)
 $621万
 $24,859/呎
-(20年-01月-05日)</t>
+(20年-01月-06日)</t>
         </is>
       </c>
       <c r="M22" s="20" t="inlineStr">
@@ -20307,7 +20307,7 @@
           <t>M | 263呎 (1房)
 $688万
 $26,172/呎
-(19年-02月-10日)</t>
+(19年-02月-11日)</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
@@ -20315,7 +20315,7 @@
           <t>N | 258呎 (1房)
 $697万
 $27,014/呎
-(18年-04月-23日)</t>
+(18年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -20330,7 +20330,7 @@
           <t>A | 365呎 (2房)
 $925万
 $25,337/呎
-(19年-03月-03日)</t>
+(19年-03月-04日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -20338,7 +20338,7 @@
           <t>B | 287呎 (1房)
 $710万
 $24,753/呎
-(21年-03月-31日)</t>
+(21年-04月-01日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -20346,7 +20346,7 @@
           <t>C | 181呎 (开放式)
 $505万
 $27,911/呎
-(18年-02月-28日)</t>
+(18年-03月-01日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -20354,7 +20354,7 @@
           <t>D | 205呎 (开放式)
 $545万
 $26,564/呎
-(19年-10月-21日)</t>
+(19年-10月-22日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -20362,7 +20362,7 @@
           <t>E | 205呎 (开放式)
 $563万
 $27,483/呎
-(19年-05月-01日)</t>
+(19年-05月-02日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -20370,7 +20370,7 @@
           <t>F | 181呎 (开放式)
 $480万
 $26,503/呎
-(19年-06月-23日)</t>
+(19年-06月-24日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -20378,7 +20378,7 @@
           <t>G | 288呎 (1房)
 $708万
 $24,567/呎
-(21年-01月-13日)</t>
+(21年-01月-14日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -20386,7 +20386,7 @@
           <t>H | 365呎 (2房)
 $912万
 $24,976/呎
-(19年-06月-27日)</t>
+(19年-06月-28日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -20394,7 +20394,7 @@
           <t>J | 258呎 (1房)
 $640万
 $24,804/呎
-(20年-02月-15日)</t>
+(20年-02月-16日)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -20402,7 +20402,7 @@
           <t>K | 257呎 (1房)
 $672万
 $26,133/呎
-(19年-05月-15日)</t>
+(19年-05月-16日)</t>
         </is>
       </c>
       <c r="L23" s="20" t="inlineStr">
@@ -20410,7 +20410,7 @@
           <t>L | 250呎 (1房)
 $630万
 $25,190/呎
-(20年-01月-01日)</t>
+(20年-01月-02日)</t>
         </is>
       </c>
       <c r="M23" s="20" t="inlineStr">
@@ -20418,7 +20418,7 @@
           <t>M | 263呎 (1房)
 $697万
 $26,515/呎
-(19年-05月-01日)</t>
+(19年-05月-02日)</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -20426,7 +20426,7 @@
           <t>N | 258呎 (1房)
 $699万
 $27,089/呎
-(18年-04月-19日)</t>
+(18年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -20441,7 +20441,7 @@
           <t>A | 365呎 (2房)
 $909万
 $24,892/呎
-(19年-01月-14日)</t>
+(19年-01月-15日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -20449,7 +20449,7 @@
           <t>B | 287呎 (1房)
 $705万
 $24,572/呎
-(21年-04月-13日)</t>
+(21年-04月-14日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -20457,7 +20457,7 @@
           <t>C | 181呎 (开放式)
 $504万
 $27,873/呎
-(18年-01月-29日)</t>
+(18年-01月-30日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -20465,7 +20465,7 @@
           <t>D | 205呎 (开放式)
 $538万
 $26,266/呎
-(19年-12月-23日)</t>
+(19年-12月-24日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -20473,7 +20473,7 @@
           <t>E | 205呎 (开放式)
 $546万
 $26,627/呎
-(19年-04月-25日)</t>
+(19年-04月-26日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -20481,7 +20481,7 @@
           <t>F | 181呎 (开放式)
 $497万
 $27,478/呎
-(19年-06月-21日)</t>
+(19年-06月-22日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -20489,7 +20489,7 @@
           <t>G | 287呎 (1房)
 $702万
 $24,472/呎
-(20年-12月-22日)</t>
+(20年-12月-23日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -20497,7 +20497,7 @@
           <t>H | 365呎 (2房)
 $914万
 $25,048/呎
-(19年-06月-27日)</t>
+(19年-06月-28日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -20505,7 +20505,7 @@
           <t>J | 258呎 (1房)
 $635万
 $24,625/呎
-(19年-12月-14日)</t>
+(19年-12月-15日)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -20513,7 +20513,7 @@
           <t>K | 257呎 (1房)
 $660万
 $25,677/呎
-(19年-05月-04日)</t>
+(19年-05月-05日)</t>
         </is>
       </c>
       <c r="L24" s="20" t="inlineStr">
@@ -20521,7 +20521,7 @@
           <t>L | 250呎 (1房)
 $612万
 $24,498/呎
-(20年-01月-05日)</t>
+(20年-01月-06日)</t>
         </is>
       </c>
       <c r="M24" s="20" t="inlineStr">
@@ -20529,7 +20529,7 @@
           <t>M | 263呎 (1房)
 $678万
 $25,784/呎
-(19年-04月-03日)</t>
+(19年-04月-04日)</t>
         </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
@@ -20537,7 +20537,7 @@
           <t>N | 258呎 (1房)
 $694万
 $26,895/呎
-(18年-02月-25日)</t>
+(18年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -20552,7 +20552,7 @@
           <t>A | 365呎 (2房)
 $902万
 $24,705/呎
-(18年-02月-26日)</t>
+(18年-02月-27日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -20560,7 +20560,7 @@
           <t>B | 287呎 (1房)
 $697万
 $24,301/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -20568,7 +20568,7 @@
           <t>C | 181呎 (开放式)
 $477万
 $26,350/呎
-(18年-02月-26日)</t>
+(18年-02月-27日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -20576,7 +20576,7 @@
           <t>D | 205呎 (开放式)
 $530万
 $25,868/呎
-(19年-10月-21日)</t>
+(19年-10月-22日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -20584,7 +20584,7 @@
           <t>E | 205呎 (开放式)
 $549万
 $26,776/呎
-(18年-10月-21日)</t>
+(18年-10月-22日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -20592,7 +20592,7 @@
           <t>F | 181呎 (开放式)
 $480万
 $26,514/呎
-(19年-07月-11日)</t>
+(19年-07月-12日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -20600,7 +20600,7 @@
           <t>G | 288呎 (1房)
 $704万
 $24,459/呎
-(20年-04月-26日)</t>
+(20年-04月-27日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -20608,7 +20608,7 @@
           <t>H | 365呎 (2房)
 $898万
 $24,609/呎
-(19年-05月-26日)</t>
+(19年-05月-27日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -20616,7 +20616,7 @@
           <t>J | 258呎 (1房)
 $657万
 $25,461/呎
-(20年-02月-09日)</t>
+(20年-02月-10日)</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -20624,7 +20624,7 @@
           <t>K | 257呎 (1房)
 $662万
 $25,752/呎
-(19年-05月-26日)</t>
+(19年-05月-27日)</t>
         </is>
       </c>
       <c r="L25" s="20" t="inlineStr">
@@ -20632,7 +20632,7 @@
           <t>L | 250呎 (1房)
 $608万
 $24,320/呎
-(20年-01月-20日)</t>
+(20年-01月-21日)</t>
         </is>
       </c>
       <c r="M25" s="20" t="inlineStr">
@@ -20640,7 +20640,7 @@
           <t>M | 263呎 (1房)
 $666万
 $25,329/呎
-(19年-04月-22日)</t>
+(19年-04月-23日)</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -20648,7 +20648,7 @@
           <t>N | 258呎 (1房)
 $661万
 $25,630/呎
-(18年-02月-14日)</t>
+(18年-02月-15日)</t>
         </is>
       </c>
     </row>
@@ -20663,7 +20663,7 @@
           <t>A | 352呎 (2房)
 $1001万
 $28,432/呎
-(20年-07月-21日)</t>
+(20年-07月-22日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -20671,7 +20671,7 @@
           <t>B | 287呎 (1房)
 $834万
 $29,068/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -20679,7 +20679,7 @@
           <t>C | 181呎 (开放式)
 $470万
 $25,941/呎
-(21年-02月-11日)</t>
+(21年-02月-12日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -20687,7 +20687,7 @@
           <t>D | 205呎 (开放式)
 $522万
 $25,471/呎
-(19年-10月-03日)</t>
+(19年-10月-04日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -20695,7 +20695,7 @@
           <t>E | 205呎 (开放式)
 $530万
 $25,831/呎
-(19年-05月-05日)</t>
+(19年-05月-06日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -20703,7 +20703,7 @@
           <t>F | 181呎 (开放式)
 $487万
 $26,921/呎
-(19年-07月-11日)</t>
+(19年-07月-12日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -20711,7 +20711,7 @@
           <t>G | 287呎 (1房)
 $834万
 $29,058/呎
-(21年-12月-13日)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -20719,7 +20719,7 @@
           <t>H | 352呎 (2房)
 $831万
 $23,600/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -20727,7 +20727,7 @@
           <t>J | 258呎 (1房)
 $643万
 $24,927/呎
-(20年-03月-02日)</t>
+(20年-03月-03日)</t>
         </is>
       </c>
       <c r="K26" s="20" t="inlineStr">
@@ -20735,7 +20735,7 @@
           <t>K | 257呎 (1房)
 $655万
 $25,469/呎
-(19年-05月-26日)</t>
+(19年-05月-27日)</t>
         </is>
       </c>
       <c r="L26" s="20" t="inlineStr">
@@ -20743,7 +20743,7 @@
           <t>L | 250呎 (1房)
 $595万
 $23,800/呎
-(20年-01月-01日)</t>
+(20年-01月-02日)</t>
         </is>
       </c>
       <c r="M26" s="20" t="inlineStr">
@@ -20751,7 +20751,7 @@
           <t>M | 263呎 (1房)
 $665万
 $25,301/呎
-(19年-04月-28日)</t>
+(19年-04月-29日)</t>
         </is>
       </c>
       <c r="N26" s="20" t="inlineStr">
@@ -20759,7 +20759,7 @@
           <t>N | 258呎 (1房)
 $654万
 $25,347/呎
-(21年-03月-16日)</t>
+(21年-03月-17日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-北角-君誉峰.xlsx
+++ b/files/港岛-北角-君誉峰.xlsx
@@ -17714,7 +17714,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -20719,7 +20719,7 @@
           <t>H | 352呎 (2房)
 $831万
 $23,600/呎
-(26年-07月-13日)</t>
+(26年-08月-12日)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">

--- a/files/港岛-北角-君誉峰.xlsx
+++ b/files/港岛-北角-君誉峰.xlsx
@@ -1023,38 +1023,30 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>15215200</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>36400</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K7" s="5" t="n">
+        <v>15215200</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>36400</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1063,7 +1055,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18260,7 +18252,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18270,7 +18262,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18386,12 +18378,12 @@
 (21年-08月-09日)</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 418呎 (2房)
-招标单位
--
-(在售)</t>
+$1522万
+$36,400/呎
+(26年-08月-27日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">

--- a/files/港岛-北角-君誉峰.xlsx
+++ b/files/港岛-北角-君誉峰.xlsx
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>15215200</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>36400</v>
+        <v>36313</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>15215200</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>36400</v>
+        <v>36313</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -18380,9 +18380,9 @@
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>D | 418呎 (2房)
+          <t>D | 419呎 (2房)
 $1522万
-$36,400/呎
+$36,313/呎
 (26年-08月-27日)</t>
         </is>
       </c>

--- a/files/港岛-北角-君誉峰.xlsx
+++ b/files/港岛-北角-君誉峰.xlsx
@@ -4185,34 +4185,34 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
-        <v>6386000</v>
+        <v>5396100</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>31151</v>
+        <v>26322</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="5" t="n">
-        <v>5396170</v>
+        <v>5396100</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>26323</v>
+        <v>26322</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃 - 90天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -18252,7 +18252,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18262,7 +18262,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>275</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18795,12 +18795,12 @@
 (21年-04月-29日)</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
-$639万
-$31,151/呎
-(在售)</t>
+$540万
+$26,322/呎
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
